--- a/IML-Cell-Process-Advisor/MAKİNE - ÜRÜN(1).xlsx
+++ b/IML-Cell-Process-Advisor/MAKİNE - ÜRÜN(1).xlsx
@@ -398,36 +398,40 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -623,1629 +627,1629 @@
   <dimension ref="B2:H80"/>
   <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="12.8"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>56.8</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2" t="n">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="3" t="n">
         <v>47295</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2" t="n">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="3" t="n">
         <v>73685</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>45232</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4"/>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>77279</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="2" t="n">
+      <c r="E9" s="5"/>
+      <c r="F9" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>1400008136</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2" t="n">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="3" t="n">
         <v>1400008137</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2" t="n">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="3" t="n">
         <v>1400008459</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>63.5</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4"/>
-      <c r="C14" s="2" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>64243</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="2" t="n">
+      <c r="E14" s="5"/>
+      <c r="F14" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4"/>
-      <c r="C15" s="2" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="2" t="n">
+      <c r="E15" s="5"/>
+      <c r="F15" s="3" t="n">
         <v>47.39</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>20790995</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="2" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="3" t="n">
         <v>47735</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="2" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="3" t="n">
         <v>46243</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <v>46241</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="5" t="n">
         <v>201</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="3" t="n">
         <v>47743</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="2" t="n">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="3" t="n">
         <v>19138</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="2" t="n">
+      <c r="E27" s="5"/>
+      <c r="F27" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="5" t="n">
         <v>202</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="5" t="n">
         <v>18.5</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="2" t="s">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="5" t="n">
         <v>203</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="3" t="n">
         <v>47743</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="2" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="3" t="s">
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="3" t="n">
         <v>64240</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="2" t="n">
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="3" t="n">
         <v>122500646</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="3" t="s">
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="3" t="n">
         <v>20721888</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="3" t="n">
         <v>81344</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="5" t="n">
         <v>8.5</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="2" t="n">
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="3" t="n">
         <v>69508</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" s="3" t="s">
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="5" t="n">
         <v>207</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="3" t="n">
         <v>12001302</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="3" t="n">
         <v>2.98</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4"/>
-      <c r="C38" s="2" t="s">
+      <c r="B38" s="5"/>
+      <c r="C38" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>45326</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="5" t="n">
         <v>301</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>13038801</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="2" t="n">
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="3" t="n">
         <v>13028518</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="2" t="s">
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H40" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="5" t="n">
         <v>302</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G41" s="2" t="s">
+      <c r="F41" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="4"/>
-      <c r="C42" s="5" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>82006</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="2" t="n">
+      <c r="E42" s="5"/>
+      <c r="F42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" s="3" t="s">
+      <c r="G42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="5" t="n">
         <v>303</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>19225</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="5" t="n">
         <v>8.5</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="2" t="n">
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="3" t="n">
         <v>19224</v>
       </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="2" t="s">
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="2" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="2" t="s">
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="4"/>
-      <c r="C47" s="6" t="s">
+      <c r="B47" s="5"/>
+      <c r="C47" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="3" t="n">
         <v>12004341</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="2" t="n">
+      <c r="B48" s="3" t="n">
         <v>305</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H48" s="3" t="s">
+      <c r="G48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="3" t="n">
         <v>306</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>92855</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="3" t="s">
+      <c r="G49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="3" t="n">
         <v>307</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="3" t="n">
         <v>13025963</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="3" t="s">
+      <c r="G50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="5" t="n">
         <v>308</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="3" t="n">
         <v>13026042</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H51" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="4"/>
-      <c r="C52" s="2" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="3" t="n">
         <v>122500647</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H52" s="3" t="s">
+      <c r="G52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="3" t="n">
         <v>309</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>44748</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H53" s="3" t="s">
+      <c r="G53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="3" t="n">
         <v>401</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="3" t="n">
         <v>19085</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H54" s="3" t="s">
+      <c r="G54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="5" t="n">
         <v>402</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>20312827</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>14</v>
+      <c r="G55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="4"/>
-      <c r="C56" s="2" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="G56" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H56" s="3" t="s">
+      <c r="G56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="3" t="n">
         <v>403</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="3" t="n">
         <v>48050</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H57" s="3" t="s">
+      <c r="G57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="3" t="n">
         <v>48254</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F58" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" s="3" t="s">
+      <c r="G58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="2" t="n">
+      <c r="B59" s="3" t="n">
         <v>405</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="3" t="n">
         <v>61569</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H59" s="3" t="s">
+      <c r="G59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="3" t="n">
         <v>406</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="3" t="n">
         <v>44637</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F60" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" s="3" t="s">
+      <c r="G60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="5" t="n">
         <v>407</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="3" t="n">
         <v>48050</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" s="3" t="s">
+      <c r="G61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="2" t="n">
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="3" t="n">
         <v>19151</v>
       </c>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H62" s="3" t="s">
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="5" t="n">
         <v>408</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H63" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="4"/>
-      <c r="C64" s="2" t="s">
+      <c r="B64" s="5"/>
+      <c r="C64" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="3" t="n">
         <v>12006621</v>
       </c>
-      <c r="E64" s="4"/>
-      <c r="F64" s="2" t="n">
+      <c r="E64" s="5"/>
+      <c r="F64" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" s="3" t="s">
+      <c r="G64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="3" t="n">
         <v>501</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H65" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="5" t="n">
         <v>502</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="3" t="n">
         <v>10.52</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H66" s="3" t="s">
+      <c r="G66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="4"/>
-      <c r="C67" s="2" t="s">
+      <c r="B67" s="5"/>
+      <c r="C67" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>13050814</v>
       </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="2" t="n">
+      <c r="E67" s="5"/>
+      <c r="F67" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H67" s="3" t="s">
+      <c r="G67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="3" t="n">
         <v>503</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="3" t="n">
         <v>20040</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F68" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" s="3" t="s">
+      <c r="G68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="5" t="n">
         <v>504</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D69" s="2" t="n">
+      <c r="D69" s="3" t="n">
         <v>47203</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="F69" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H69" s="3" t="s">
+      <c r="G69" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="4"/>
-      <c r="C70" s="2" t="s">
+      <c r="B70" s="5"/>
+      <c r="C70" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E70" s="4"/>
-      <c r="F70" s="2" t="n">
+      <c r="E70" s="5"/>
+      <c r="F70" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H70" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="4" t="n">
+      <c r="B71" s="5" t="n">
         <v>505</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D71" s="3" t="n">
         <v>47840</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="5" t="n">
         <v>8.5</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" s="3" t="s">
+      <c r="G71" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="2" t="n">
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="3" t="n">
         <v>45138</v>
       </c>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H72" s="3" t="s">
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="5" t="n">
         <v>506</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D73" s="2" t="n">
+      <c r="D73" s="3" t="n">
         <v>20804595</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F73" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H73" s="3" t="s">
+      <c r="G73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="4"/>
-      <c r="C74" s="2" t="s">
+      <c r="B74" s="5"/>
+      <c r="C74" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D74" s="3" t="n">
         <v>64239</v>
       </c>
-      <c r="E74" s="4"/>
-      <c r="F74" s="2" t="n">
+      <c r="E74" s="5"/>
+      <c r="F74" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H74" s="3" t="s">
+      <c r="G74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="5" t="n">
         <v>507</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="2" t="n">
+      <c r="D75" s="3" t="n">
         <v>76063057</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="F75" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H75" s="3" t="s">
+      <c r="G75" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="4"/>
-      <c r="C76" s="2" t="s">
+      <c r="B76" s="5"/>
+      <c r="C76" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="3" t="n">
         <v>12004339</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H76" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="5" t="n">
         <v>508</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D77" s="2" t="n">
+      <c r="D77" s="3" t="n">
         <v>20823003</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="3" t="n">
         <v>17.37</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H77" s="3" t="s">
+      <c r="G77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="4"/>
-      <c r="C78" s="2" t="s">
+      <c r="B78" s="5"/>
+      <c r="C78" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D78" s="2" t="n">
+      <c r="D78" s="3" t="n">
         <v>47385</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F78" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H78" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="5" t="n">
         <v>509</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D79" s="2" t="n">
+      <c r="D79" s="3" t="n">
         <v>13050918</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E79" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F79" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="3" t="s">
+      <c r="G79" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="4"/>
-      <c r="C80" s="2" t="s">
+      <c r="B80" s="5"/>
+      <c r="C80" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D80" s="2" t="n">
+      <c r="D80" s="3" t="n">
         <v>48034</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E80" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F80" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="H80" s="4" t="s">
         <v>14</v>
       </c>
     </row>
